--- a/artfynd/A 40274-2022 artfynd.xlsx
+++ b/artfynd/A 40274-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40274-2022 artfynd.xlsx
+++ b/artfynd/A 40274-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104340280</v>
+        <v>112502131</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577150.1062916896</v>
+        <v>577255</v>
       </c>
       <c r="R2" t="n">
-        <v>7056746.676073044</v>
+        <v>7056664</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,27 +771,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104340200</v>
+        <v>112330611</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,35 +794,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Lill-Svarttjärnen, Lill-Svarttjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577144.2972259929</v>
+        <v>577248</v>
       </c>
       <c r="R3" t="n">
-        <v>7056729.189081476</v>
+        <v>7056660</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,22 +849,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,49 +879,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104340304</v>
+        <v>104340100</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577159.408500094</v>
+        <v>577250</v>
       </c>
       <c r="R4" t="n">
-        <v>7056730.446586247</v>
+        <v>7056661</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,19 +999,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104340270</v>
+        <v>104339692</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1055,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577150.1062916896</v>
+        <v>577246</v>
       </c>
       <c r="R5" t="n">
-        <v>7056746.676073044</v>
+        <v>7056677</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1068,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,12 +1085,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1130,16 +1100,11 @@
         <v>104340028</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1168,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577258.8340089077</v>
+        <v>577259</v>
       </c>
       <c r="R6" t="n">
-        <v>7056671.047486454</v>
+        <v>7056671</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1240,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104340353</v>
+        <v>104340203</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577180.5213158859</v>
+        <v>577145</v>
       </c>
       <c r="R7" t="n">
-        <v>7056704.719976875</v>
+        <v>7056730</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,19 +1313,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104339692</v>
+        <v>104340270</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1394,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577245.7853870327</v>
+        <v>577150</v>
       </c>
       <c r="R8" t="n">
-        <v>7056676.511294631</v>
+        <v>7056746</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1429,7 +1384,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1394,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,27 +1409,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104340293</v>
+        <v>112331359</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,35 +1432,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Bodhöjden, Bodhöjden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577158.9646620895</v>
+        <v>577102</v>
       </c>
       <c r="R9" t="n">
-        <v>7056748.670824193</v>
+        <v>7056694</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1537,22 +1487,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,63 +1517,58 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104340100</v>
+        <v>112330621</v>
       </c>
       <c r="B10" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Bodhöjden, Bodhöjden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577250.18139662</v>
+        <v>577256</v>
       </c>
       <c r="R10" t="n">
-        <v>7056660.606833535</v>
+        <v>7056659</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,22 +1595,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,27 +1625,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104340203</v>
+        <v>104340200</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,21 +1648,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577144.2972259929</v>
+        <v>577145</v>
       </c>
       <c r="R11" t="n">
-        <v>7056729.189081476</v>
+        <v>7056730</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,15 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112330621</v>
+        <v>112502508</v>
       </c>
       <c r="B12" t="n">
-        <v>77441</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,35 +1756,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodhöjden (Bodhöjden), Ång</t>
+          <t>Bodhöjden, Bodhöjden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577256</v>
+        <v>577213</v>
       </c>
       <c r="R12" t="n">
-        <v>7056659</v>
+        <v>7056665</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1876,22 +1816,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,15 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112331359</v>
+        <v>112502528</v>
       </c>
       <c r="B13" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,35 +1869,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodhöjden (Bodhöjden), Ång</t>
+          <t>Bodhöjden, Bodhöjden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577102</v>
+        <v>577213</v>
       </c>
       <c r="R13" t="n">
-        <v>7056694</v>
+        <v>7056687</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1989,22 +1929,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,63 +1959,63 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112330627</v>
+        <v>112502199</v>
       </c>
       <c r="B14" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bodhöjden (Bodhöjden), Ång</t>
+          <t>Bodhöjden, Bodhöjden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577251</v>
+        <v>577201</v>
       </c>
       <c r="R14" t="n">
-        <v>7056656</v>
+        <v>7056615</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2102,22 +2042,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,51 +2084,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112330611</v>
+        <v>104340280</v>
       </c>
       <c r="B15" t="n">
-        <v>89594</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Svarttjärnen (Lill-Svarttjärnen), Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577247</v>
+        <v>577150</v>
       </c>
       <c r="R15" t="n">
-        <v>7056660</v>
+        <v>7056746</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,22 +2150,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,27 +2180,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112331735</v>
+        <v>104340293</v>
       </c>
       <c r="B16" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2294,14 +2224,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bodhöjden (Bodhöjden), Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577158</v>
+        <v>577159</v>
       </c>
       <c r="R16" t="n">
-        <v>7056757</v>
+        <v>7056749</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,22 +2258,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,27 +2278,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112331647</v>
+        <v>104340304</v>
       </c>
       <c r="B17" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2403,22 +2318,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bodhöjden (Bodhöjden), Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577150</v>
+        <v>577159</v>
       </c>
       <c r="R17" t="n">
-        <v>7056741</v>
+        <v>7056730</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2445,22 +2356,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2475,27 +2376,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112331811</v>
+        <v>104340353</v>
       </c>
       <c r="B18" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,22 +2416,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sollefteå (Sollefteå), Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577158</v>
+        <v>577181</v>
       </c>
       <c r="R18" t="n">
-        <v>7056738</v>
+        <v>7056705</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,22 +2454,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,27 +2474,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112502371</v>
+        <v>112330627</v>
       </c>
       <c r="B19" t="n">
-        <v>96853</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,22 +2514,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bodhöjden (Bodhöjden), Ång</t>
+          <t>Bodhöjden, Bodhöjden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577167</v>
+        <v>577251</v>
       </c>
       <c r="R19" t="n">
-        <v>7056735</v>
+        <v>7056656</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,22 +2552,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,51 +2594,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112502131</v>
+        <v>112331647</v>
       </c>
       <c r="B20" t="n">
-        <v>89942</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sollefteå (Sollefteå), Ång</t>
+          <t>Bodhöjden, Bodhöjden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577255</v>
+        <v>577150</v>
       </c>
       <c r="R20" t="n">
-        <v>7056664</v>
+        <v>7056742</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2792,22 +2664,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,68 +2694,58 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112502528</v>
+        <v>112331735</v>
       </c>
       <c r="B21" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bodhöjden (Bodhöjden), Ång</t>
+          <t>Bodhöjden, Bodhöjden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577213</v>
+        <v>577158</v>
       </c>
       <c r="R21" t="n">
-        <v>7056687</v>
+        <v>7056756</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2910,22 +2772,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,68 +2802,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112502199</v>
+        <v>112331811</v>
       </c>
       <c r="B22" t="n">
-        <v>56658</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bodhöjden (Bodhöjden), Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577202</v>
+        <v>577158</v>
       </c>
       <c r="R22" t="n">
-        <v>7056615</v>
+        <v>7056738</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3028,22 +2884,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3058,15 +2914,225 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>112502371</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bodhöjden, Bodhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>577167</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7056735</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>104340489</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>577216</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7056676</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jonatan Nordström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jonatan Nordström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40274-2022 artfynd.xlsx
+++ b/artfynd/A 40274-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112502131</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112330611</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104340100</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104339692</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104340028</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104340203</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104340270</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112331359</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112330621</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104340200</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1855,6 +1910,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112502508</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112502528</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2081,6 +2146,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112502199</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2189,6 +2259,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104340280</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2287,6 +2362,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104340293</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2385,6 +2465,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104340304</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2483,6 +2568,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104340353</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2591,6 +2681,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112330627</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2703,6 +2798,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112331647</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2811,6 +2911,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112331735</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2923,6 +3028,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112331811</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3035,6 +3145,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112502371</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,8 +3248,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104340489</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>